--- a/docs/ophir/ophir-10k-18k-gram-maliyet.xlsx
+++ b/docs/ophir/ophir-10k-18k-gram-maliyet.xlsx
@@ -451,28 +451,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>OPHIR 93 LISTING — US 7 referansinda gram ve uretici maliyeti (USD). Diger bedenler panelde (36.784 varyant, weight_grams).</t>
+          <t>OPHIR 93 LISTING — US 7 referansinda gram ve uretici maliyeti (USD). Sivrilen yuzukte en = (ust+shank)/2 (sahibin kurali, 2026-09-16). Diger bedenler panelde (36.784 varyant).</t>
         </is>
       </c>
     </row>
@@ -509,35 +510,40 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Etkin en mm</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>Kalinlik mm</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>10K g</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>14K g</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>18K g</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>10K $</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>14K $ (uretici)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>18K $</t>
         </is>
@@ -557,7 +563,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -567,25 +573,28 @@
         <v>3.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>6.72</v>
+        <v>7.25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>7.529</v>
+        <v>7.741</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>8.561</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>516.5599999999999</v>
+        <v>8.673999999999999</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>9.862</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>752.9</v>
+        <v>595.04</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>1049.44</v>
+        <v>867.4</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>1208.92</v>
       </c>
     </row>
     <row r="4">
@@ -609,24 +618,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="L4" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="N4" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
@@ -651,24 +663,27 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>2.135</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>2.393</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>2.721</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="L5" s="7" t="n">
         <v>164.12</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="7" t="n">
         <v>239.3</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>333.55</v>
       </c>
     </row>
@@ -693,24 +708,27 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>4.271</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>4.785</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>5.441</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="L6" s="7" t="n">
         <v>328.31</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>478.5</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>666.98</v>
       </c>
     </row>
@@ -735,24 +753,27 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>4.271</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>4.785</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>5.441</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="L7" s="7" t="n">
         <v>328.31</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="7" t="n">
         <v>478.5</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="7" t="n">
         <v>666.98</v>
       </c>
     </row>
@@ -780,24 +801,27 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="6" t="n">
         <v>4.271</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>4.785</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>5.441</v>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="L8" s="7" t="n">
         <v>328.31</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="7" t="n">
         <v>478.5</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="N8" s="7" t="n">
         <v>666.98</v>
       </c>
     </row>
@@ -822,24 +846,27 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>6.406</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>7.178</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>8.162000000000001</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="L9" s="7" t="n">
         <v>492.42</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>717.8</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="N9" s="7" t="n">
         <v>1000.53</v>
       </c>
     </row>
@@ -864,24 +891,27 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>6.406</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>7.178</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>8.162000000000001</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>492.42</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>717.8</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>1000.53</v>
       </c>
     </row>
@@ -906,24 +936,27 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>7.474</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>8.374000000000001</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>9.522</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="L11" s="7" t="n">
         <v>574.52</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="M11" s="7" t="n">
         <v>837.4</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="N11" s="7" t="n">
         <v>1167.24</v>
       </c>
     </row>
@@ -948,24 +981,27 @@
         <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H12" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>3.31</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>3.709</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>4.217</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="L12" s="7" t="n">
         <v>254.44</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="M12" s="7" t="n">
         <v>370.9</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="N12" s="7" t="n">
         <v>516.9299999999999</v>
       </c>
     </row>
@@ -993,24 +1029,27 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H13" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="6" t="n">
         <v>2.669</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>2.991</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>3.401</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="L13" s="7" t="n">
         <v>205.16</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="7" t="n">
         <v>299.1</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="N13" s="7" t="n">
         <v>416.91</v>
       </c>
     </row>
@@ -1035,24 +1074,27 @@
         <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H14" s="6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>2.082</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>2.333</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>2.653</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="L14" s="7" t="n">
         <v>160.04</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="7" t="n">
         <v>233.3</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="N14" s="7" t="n">
         <v>325.21</v>
       </c>
     </row>
@@ -1077,24 +1119,27 @@
         <v>1.45</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H15" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>1.548</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>1.735</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>1.972</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="L15" s="7" t="n">
         <v>118.99</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="M15" s="7" t="n">
         <v>173.5</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="N15" s="7" t="n">
         <v>241.73</v>
       </c>
     </row>
@@ -1112,7 +1157,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1122,25 +1167,28 @@
         <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.49</v>
+        <v>1.868</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.694</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>102.24</v>
+        <v>2.094</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>2.381</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>149</v>
+        <v>143.59</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>207.66</v>
+        <v>209.4</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>291.87</v>
       </c>
     </row>
     <row r="17">
@@ -1167,24 +1215,27 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H17" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="6" t="n">
         <v>1.174</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>1.316</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>1.496</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="L17" s="7" t="n">
         <v>90.23999999999999</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="M17" s="7" t="n">
         <v>131.6</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="N17" s="7" t="n">
         <v>183.38</v>
       </c>
     </row>
@@ -1212,24 +1263,27 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="L18" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="M18" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="N18" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
@@ -1247,7 +1301,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1257,25 +1311,28 @@
         <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1.496</v>
+        <v>1.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.5</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.677</v>
+        <v>2.029</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.907</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>115</v>
+        <v>2.273</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>2.585</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>167.7</v>
+        <v>155.97</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>233.77</v>
+        <v>227.3</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>316.88</v>
       </c>
     </row>
     <row r="20">
@@ -1299,24 +1356,27 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H20" s="6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I20" s="6" t="n">
         <v>10.356</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>11.605</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>13.195</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="L20" s="7" t="n">
         <v>796.0599999999999</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="M20" s="7" t="n">
         <v>1160.5</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="N20" s="7" t="n">
         <v>1617.49</v>
       </c>
     </row>
@@ -1341,24 +1401,27 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I21" s="6" t="n">
         <v>4.271</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>4.785</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>5.441</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="L21" s="7" t="n">
         <v>328.31</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="M21" s="7" t="n">
         <v>478.5</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="N21" s="7" t="n">
         <v>666.98</v>
       </c>
     </row>
@@ -1383,24 +1446,27 @@
         <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H22" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="6" t="n">
         <v>2.776</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>3.111</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>3.537</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="L22" s="7" t="n">
         <v>213.39</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="M22" s="7" t="n">
         <v>311.1</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="N22" s="7" t="n">
         <v>433.58</v>
       </c>
     </row>
@@ -1425,24 +1491,27 @@
         <v>3.6</v>
       </c>
       <c r="G23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.6</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>4.1</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>4.594</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>5.224</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="L23" s="7" t="n">
         <v>315.16</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="M23" s="7" t="n">
         <v>459.4</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="N23" s="7" t="n">
         <v>640.38</v>
       </c>
     </row>
@@ -1467,24 +1536,27 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>3.203</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>3.589</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>4.081</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="L24" s="7" t="n">
         <v>246.21</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="M24" s="7" t="n">
         <v>358.9</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="N24" s="7" t="n">
         <v>500.26</v>
       </c>
     </row>
@@ -1512,24 +1584,27 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>3.203</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>3.589</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>4.081</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="L25" s="7" t="n">
         <v>246.21</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="M25" s="7" t="n">
         <v>358.9</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="N25" s="7" t="n">
         <v>500.26</v>
       </c>
     </row>
@@ -1547,7 +1622,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1557,25 +1632,28 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>8.500999999999999</v>
+        <v>8.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>9.525</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>653.46</v>
+        <v>10.169</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>11.562</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>952.5</v>
+        <v>697.59</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1327.58</v>
+        <v>1016.9</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>1417.31</v>
       </c>
     </row>
     <row r="27">
@@ -1599,24 +1677,27 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I27" s="6" t="n">
         <v>3.203</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>3.589</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>4.081</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="L27" s="7" t="n">
         <v>246.21</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="7" t="n">
         <v>358.9</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="N27" s="7" t="n">
         <v>500.26</v>
       </c>
     </row>
@@ -1641,24 +1722,27 @@
         <v>4.45</v>
       </c>
       <c r="G28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I28" s="6" t="n">
         <v>4.751</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="J28" s="6" t="n">
         <v>5.324</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>6.053</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="L28" s="7" t="n">
         <v>365.21</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="7" t="n">
         <v>532.4</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="N28" s="7" t="n">
         <v>742</v>
       </c>
     </row>
@@ -1676,7 +1760,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1686,25 +1770,28 @@
         <v>1.65</v>
       </c>
       <c r="G29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>2.561</v>
+        <v>3.625</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.5</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2.87</v>
+        <v>3.87</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3.263</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>196.86</v>
+        <v>4.337</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>4.931</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>287</v>
+        <v>297.48</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>399.99</v>
+        <v>433.7</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>604.46</v>
       </c>
     </row>
     <row r="30">
@@ -1728,24 +1815,27 @@
         <v>9.35</v>
       </c>
       <c r="G30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="6" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" s="6" t="n">
         <v>9.983000000000001</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>11.186</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>12.719</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="L30" s="7" t="n">
         <v>767.38</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="M30" s="7" t="n">
         <v>1118.6</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="N30" s="7" t="n">
         <v>1559.14</v>
       </c>
     </row>
@@ -1770,24 +1860,27 @@
         <v>2.8</v>
       </c>
       <c r="G31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H31" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>2.989</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>3.35</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>3.809</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="L31" s="7" t="n">
         <v>229.76</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="M31" s="7" t="n">
         <v>335</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="N31" s="7" t="n">
         <v>466.92</v>
       </c>
     </row>
@@ -1812,24 +1905,27 @@
         <v>6.35</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H32" s="6" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I32" s="6" t="n">
         <v>6.78</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="J32" s="6" t="n">
         <v>7.597</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>8.638</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="L32" s="7" t="n">
         <v>521.17</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="M32" s="7" t="n">
         <v>759.7</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="N32" s="7" t="n">
         <v>1058.88</v>
       </c>
     </row>
@@ -1854,24 +1950,27 @@
         <v>6.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H33" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I33" s="6" t="n">
         <v>6.62</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="J33" s="6" t="n">
         <v>7.417</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>8.433999999999999</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="L33" s="7" t="n">
         <v>508.87</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="M33" s="7" t="n">
         <v>741.7</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="N33" s="7" t="n">
         <v>1033.87</v>
       </c>
     </row>
@@ -1889,7 +1988,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1899,25 +1998,28 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>3.115</v>
+        <v>4.15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.5</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>3.49</v>
+        <v>4.431</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3.968</v>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>239.45</v>
+        <v>4.965</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>5.645</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>349</v>
+        <v>340.61</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>486.41</v>
+        <v>496.5</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>691.98</v>
       </c>
     </row>
     <row r="35">
@@ -1941,24 +2043,27 @@
         <v>5.8</v>
       </c>
       <c r="G35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H35" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I35" s="6" t="n">
         <v>6.193</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="J35" s="6" t="n">
         <v>6.939</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="6" t="n">
         <v>7.89</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="L35" s="7" t="n">
         <v>476.05</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="M35" s="7" t="n">
         <v>693.9</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="N35" s="7" t="n">
         <v>967.1799999999999</v>
       </c>
     </row>
@@ -1985,22 +2090,25 @@
       <c r="G36" t="n">
         <v>1.5</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I36" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="J36" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="L36" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="M36" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="N36" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -2018,7 +2126,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2028,25 +2136,28 @@
         <v>1.7</v>
       </c>
       <c r="G37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>7.126</v>
+        <v>7.35</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.5</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7.985</v>
+        <v>7.847</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>9.079000000000001</v>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>547.77</v>
+        <v>8.792999999999999</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>9.997999999999999</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>798.5</v>
+        <v>603.1900000000001</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>1112.93</v>
+        <v>879.3</v>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>1225.59</v>
       </c>
     </row>
     <row r="38">
@@ -2070,24 +2181,27 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I38" s="6" t="n">
         <v>2.135</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="J38" s="6" t="n">
         <v>2.393</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>2.721</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="L38" s="7" t="n">
         <v>164.12</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="M38" s="7" t="n">
         <v>239.3</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="N38" s="7" t="n">
         <v>333.55</v>
       </c>
     </row>
@@ -2114,22 +2228,25 @@
       <c r="G39" t="n">
         <v>1.5</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I39" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="L39" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="M39" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="N39" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -2154,24 +2271,27 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="J40" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="L40" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="M40" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="N40" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
@@ -2189,7 +2309,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2199,25 +2319,28 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>3.401</v>
+        <v>4.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.5</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>3.811</v>
+        <v>4.805</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>261.43</v>
+        <v>5.384</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>6.121</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>381.1</v>
+        <v>369.36</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>531.15</v>
+        <v>538.4</v>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>750.33</v>
       </c>
     </row>
     <row r="42">
@@ -2241,24 +2364,27 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H42" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I42" s="6" t="n">
         <v>10.463</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="J42" s="6" t="n">
         <v>11.724</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="6" t="n">
         <v>13.331</v>
       </c>
-      <c r="K42" s="7" t="n">
+      <c r="L42" s="7" t="n">
         <v>804.28</v>
       </c>
-      <c r="L42" s="7" t="n">
+      <c r="M42" s="7" t="n">
         <v>1172.4</v>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="N42" s="7" t="n">
         <v>1634.16</v>
       </c>
     </row>
@@ -2283,24 +2409,27 @@
         <v>2.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H43" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I43" s="6" t="n">
         <v>2.989</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="J43" s="6" t="n">
         <v>3.35</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="6" t="n">
         <v>3.809</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="L43" s="7" t="n">
         <v>229.76</v>
       </c>
-      <c r="L43" s="7" t="n">
+      <c r="M43" s="7" t="n">
         <v>335</v>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="N43" s="7" t="n">
         <v>466.92</v>
       </c>
     </row>
@@ -2325,24 +2454,27 @@
         <v>2.5</v>
       </c>
       <c r="G44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H44" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I44" s="6" t="n">
         <v>2.669</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="J44" s="6" t="n">
         <v>2.991</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="6" t="n">
         <v>3.401</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="L44" s="7" t="n">
         <v>205.16</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="M44" s="7" t="n">
         <v>299.1</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="N44" s="7" t="n">
         <v>416.91</v>
       </c>
     </row>
@@ -2370,24 +2502,27 @@
         <v>1.6</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H45" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I45" s="6" t="n">
         <v>1.708</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="J45" s="6" t="n">
         <v>1.914</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="6" t="n">
         <v>2.176</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="L45" s="7" t="n">
         <v>131.29</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="M45" s="7" t="n">
         <v>191.4</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="N45" s="7" t="n">
         <v>266.74</v>
       </c>
     </row>
@@ -2412,24 +2547,27 @@
         <v>3.4</v>
       </c>
       <c r="G46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H46" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I46" s="6" t="n">
         <v>3.63</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="J46" s="6" t="n">
         <v>4.068</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="K46" s="6" t="n">
         <v>4.625</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="L46" s="7" t="n">
         <v>279.04</v>
       </c>
-      <c r="L46" s="7" t="n">
+      <c r="M46" s="7" t="n">
         <v>406.8</v>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="N46" s="7" t="n">
         <v>566.95</v>
       </c>
     </row>
@@ -2454,24 +2592,27 @@
         <v>2.9</v>
       </c>
       <c r="G47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H47" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I47" s="6" t="n">
         <v>3.096</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="J47" s="6" t="n">
         <v>3.469</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="K47" s="6" t="n">
         <v>3.945</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="L47" s="7" t="n">
         <v>237.99</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="M47" s="7" t="n">
         <v>346.9</v>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="N47" s="7" t="n">
         <v>483.59</v>
       </c>
     </row>
@@ -2499,24 +2640,27 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I48" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="J48" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="K48" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="L48" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L48" s="7" t="n">
+      <c r="M48" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="N48" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
@@ -2541,24 +2685,27 @@
         <v>3.3</v>
       </c>
       <c r="G49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H49" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I49" s="6" t="n">
         <v>3.523</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="J49" s="6" t="n">
         <v>3.948</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="K49" s="6" t="n">
         <v>4.489</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="L49" s="7" t="n">
         <v>270.81</v>
       </c>
-      <c r="L49" s="7" t="n">
+      <c r="M49" s="7" t="n">
         <v>394.8</v>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="N49" s="7" t="n">
         <v>550.28</v>
       </c>
     </row>
@@ -2583,24 +2730,27 @@
         <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I50" s="6" t="n">
         <v>3.203</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="J50" s="6" t="n">
         <v>3.589</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="K50" s="6" t="n">
         <v>4.081</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="L50" s="7" t="n">
         <v>246.21</v>
       </c>
-      <c r="L50" s="7" t="n">
+      <c r="M50" s="7" t="n">
         <v>358.9</v>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="N50" s="7" t="n">
         <v>500.26</v>
       </c>
     </row>
@@ -2625,24 +2775,27 @@
         <v>1.3</v>
       </c>
       <c r="G51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H51" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I51" s="6" t="n">
         <v>1.388</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="J51" s="6" t="n">
         <v>1.555</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="K51" s="6" t="n">
         <v>1.768</v>
       </c>
-      <c r="K51" s="7" t="n">
+      <c r="L51" s="7" t="n">
         <v>106.69</v>
       </c>
-      <c r="L51" s="7" t="n">
+      <c r="M51" s="7" t="n">
         <v>155.5</v>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="N51" s="7" t="n">
         <v>216.73</v>
       </c>
     </row>
@@ -2667,24 +2820,27 @@
         <v>2.3</v>
       </c>
       <c r="G52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H52" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I52" s="6" t="n">
         <v>2.456</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="J52" s="6" t="n">
         <v>2.752</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="K52" s="6" t="n">
         <v>3.129</v>
       </c>
-      <c r="K52" s="7" t="n">
+      <c r="L52" s="7" t="n">
         <v>188.79</v>
       </c>
-      <c r="L52" s="7" t="n">
+      <c r="M52" s="7" t="n">
         <v>275.2</v>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="N52" s="7" t="n">
         <v>383.56</v>
       </c>
     </row>
@@ -2702,7 +2858,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2712,25 +2868,28 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>3.482</v>
+        <v>4.75</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.5</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>3.901</v>
+        <v>5.071</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>4.436</v>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>267.66</v>
+        <v>5.683</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>6.461</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>390.1</v>
+        <v>389.8</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>543.78</v>
+        <v>568.3</v>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>792.01</v>
       </c>
     </row>
     <row r="54">
@@ -2759,22 +2918,25 @@
       <c r="G54" t="n">
         <v>1.5</v>
       </c>
-      <c r="H54" s="6" t="n">
+      <c r="H54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I54" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I54" s="6" t="n">
+      <c r="J54" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="K54" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K54" s="7" t="n">
+      <c r="L54" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L54" s="7" t="n">
+      <c r="M54" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="N54" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -2792,7 +2954,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2802,25 +2964,28 @@
         <v>1.8</v>
       </c>
       <c r="G55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>3.238</v>
+        <v>4.4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.5</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>3.628</v>
+        <v>4.698</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>4.125</v>
-      </c>
-      <c r="K55" s="7" t="n">
-        <v>248.9</v>
+        <v>5.264</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>5.985</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>362.8</v>
+        <v>361.13</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>505.66</v>
+        <v>526.4</v>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>733.66</v>
       </c>
     </row>
     <row r="56">
@@ -2837,7 +3002,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2847,25 +3012,28 @@
         <v>2.5</v>
       </c>
       <c r="G56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.5</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>4.773</v>
+        <v>5.605</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>5.427</v>
-      </c>
-      <c r="K56" s="7" t="n">
-        <v>327.46</v>
+        <v>6.281</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>7.142</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>477.3</v>
+        <v>430.85</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>665.26</v>
+        <v>628.1</v>
+      </c>
+      <c r="N56" s="7" t="n">
+        <v>875.49</v>
       </c>
     </row>
     <row r="57">
@@ -2882,7 +3050,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2892,25 +3060,28 @@
         <v>1.25</v>
       </c>
       <c r="G57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>4.041</v>
+        <v>5.275</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.5</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>4.528</v>
+        <v>5.632</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>5.149</v>
-      </c>
-      <c r="K57" s="7" t="n">
-        <v>310.63</v>
+        <v>6.311</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>7.176</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>452.8</v>
+        <v>432.93</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>631.1799999999999</v>
+        <v>631.1</v>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>879.66</v>
       </c>
     </row>
     <row r="58">
@@ -2937,24 +3108,27 @@
         <v>1.7</v>
       </c>
       <c r="G58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H58" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I58" s="6" t="n">
         <v>1.815</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="J58" s="6" t="n">
         <v>2.034</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="K58" s="6" t="n">
         <v>2.312</v>
       </c>
-      <c r="K58" s="7" t="n">
+      <c r="L58" s="7" t="n">
         <v>139.52</v>
       </c>
-      <c r="L58" s="7" t="n">
+      <c r="M58" s="7" t="n">
         <v>203.4</v>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="N58" s="7" t="n">
         <v>283.41</v>
       </c>
     </row>
@@ -2979,24 +3153,27 @@
         <v>3.1</v>
       </c>
       <c r="G59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H59" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I59" s="6" t="n">
         <v>3.31</v>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="J59" s="6" t="n">
         <v>3.709</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="K59" s="6" t="n">
         <v>4.217</v>
       </c>
-      <c r="K59" s="7" t="n">
+      <c r="L59" s="7" t="n">
         <v>254.44</v>
       </c>
-      <c r="L59" s="7" t="n">
+      <c r="M59" s="7" t="n">
         <v>370.9</v>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="N59" s="7" t="n">
         <v>516.9299999999999</v>
       </c>
     </row>
@@ -3021,24 +3198,27 @@
         <v>1.3</v>
       </c>
       <c r="G60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H60" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>1.388</v>
       </c>
-      <c r="I60" s="6" t="n">
+      <c r="J60" s="6" t="n">
         <v>1.555</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="K60" s="6" t="n">
         <v>1.768</v>
       </c>
-      <c r="K60" s="7" t="n">
+      <c r="L60" s="7" t="n">
         <v>106.69</v>
       </c>
-      <c r="L60" s="7" t="n">
+      <c r="M60" s="7" t="n">
         <v>155.5</v>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="N60" s="7" t="n">
         <v>216.73</v>
       </c>
     </row>
@@ -3063,24 +3243,27 @@
         <v>6.5</v>
       </c>
       <c r="G61" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H61" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I61" s="6" t="n">
         <v>6.94</v>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="J61" s="6" t="n">
         <v>7.776</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="K61" s="6" t="n">
         <v>8.842000000000001</v>
       </c>
-      <c r="K61" s="7" t="n">
+      <c r="L61" s="7" t="n">
         <v>533.47</v>
       </c>
-      <c r="L61" s="7" t="n">
+      <c r="M61" s="7" t="n">
         <v>777.6</v>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="N61" s="7" t="n">
         <v>1083.88</v>
       </c>
     </row>
@@ -3105,24 +3288,27 @@
         <v>2.3</v>
       </c>
       <c r="G62" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H62" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I62" s="6" t="n">
         <v>2.456</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="J62" s="6" t="n">
         <v>2.752</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="K62" s="6" t="n">
         <v>3.129</v>
       </c>
-      <c r="K62" s="7" t="n">
+      <c r="L62" s="7" t="n">
         <v>188.79</v>
       </c>
-      <c r="L62" s="7" t="n">
+      <c r="M62" s="7" t="n">
         <v>275.2</v>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="N62" s="7" t="n">
         <v>383.56</v>
       </c>
     </row>
@@ -3140,7 +3326,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3150,25 +3336,28 @@
         <v>1.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>1.692</v>
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.5</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.896</v>
+        <v>2.135</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>2.156</v>
-      </c>
-      <c r="K63" s="7" t="n">
-        <v>130.06</v>
+        <v>2.393</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>2.721</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>189.6</v>
+        <v>164.12</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>264.29</v>
+        <v>239.3</v>
+      </c>
+      <c r="N63" s="7" t="n">
+        <v>333.55</v>
       </c>
     </row>
     <row r="64">
@@ -3195,24 +3384,27 @@
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H64" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I64" s="6" t="n">
         <v>6.406</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="J64" s="6" t="n">
         <v>7.178</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="K64" s="6" t="n">
         <v>8.162000000000001</v>
       </c>
-      <c r="K64" s="7" t="n">
+      <c r="L64" s="7" t="n">
         <v>492.42</v>
       </c>
-      <c r="L64" s="7" t="n">
+      <c r="M64" s="7" t="n">
         <v>717.8</v>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="N64" s="7" t="n">
         <v>1000.53</v>
       </c>
     </row>
@@ -3237,24 +3429,27 @@
         <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H65" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I65" s="6" t="n">
         <v>3.203</v>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="J65" s="6" t="n">
         <v>3.589</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="K65" s="6" t="n">
         <v>4.081</v>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="L65" s="7" t="n">
         <v>246.21</v>
       </c>
-      <c r="L65" s="7" t="n">
+      <c r="M65" s="7" t="n">
         <v>358.9</v>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="N65" s="7" t="n">
         <v>500.26</v>
       </c>
     </row>
@@ -3272,7 +3467,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3282,25 +3477,28 @@
         <v>1.6</v>
       </c>
       <c r="G66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>2.323</v>
+        <v>3.3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.5</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>2.603</v>
+        <v>3.523</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K66" s="7" t="n">
-        <v>178.57</v>
+        <v>3.948</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>4.489</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>260.3</v>
+        <v>270.81</v>
       </c>
       <c r="M66" s="7" t="n">
-        <v>362.85</v>
+        <v>394.8</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>550.28</v>
       </c>
     </row>
     <row r="67">
@@ -3317,7 +3515,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3327,25 +3525,28 @@
         <v>1.6</v>
       </c>
       <c r="G67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.5</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>2.084</v>
+        <v>2.456</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="K67" s="7" t="n">
-        <v>142.98</v>
+        <v>2.752</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>3.129</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>208.4</v>
+        <v>188.79</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>290.52</v>
+        <v>275.2</v>
+      </c>
+      <c r="N67" s="7" t="n">
+        <v>383.56</v>
       </c>
     </row>
     <row r="68">
@@ -3369,24 +3570,27 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H68" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I68" s="6" t="n">
         <v>2.135</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="J68" s="6" t="n">
         <v>2.393</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="K68" s="6" t="n">
         <v>2.721</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="L68" s="7" t="n">
         <v>164.12</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="M68" s="7" t="n">
         <v>239.3</v>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="N68" s="7" t="n">
         <v>333.55</v>
       </c>
     </row>
@@ -3404,7 +3608,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3414,25 +3618,28 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>2.152</v>
+        <v>3.5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.5</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>2.412</v>
+        <v>3.737</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="K69" s="7" t="n">
-        <v>165.42</v>
+        <v>4.187</v>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>4.761</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>241.2</v>
+        <v>287.26</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>336.12</v>
+        <v>418.7</v>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>583.62</v>
       </c>
     </row>
     <row r="70">
@@ -3456,24 +3663,27 @@
         <v>5.8</v>
       </c>
       <c r="G70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H70" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I70" s="6" t="n">
         <v>6.193</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="J70" s="6" t="n">
         <v>6.939</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="K70" s="6" t="n">
         <v>7.89</v>
       </c>
-      <c r="K70" s="7" t="n">
+      <c r="L70" s="7" t="n">
         <v>476.05</v>
       </c>
-      <c r="L70" s="7" t="n">
+      <c r="M70" s="7" t="n">
         <v>693.9</v>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="N70" s="7" t="n">
         <v>967.1799999999999</v>
       </c>
     </row>
@@ -3498,24 +3708,27 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I71" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="J71" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="K71" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="L71" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L71" s="7" t="n">
+      <c r="M71" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="N71" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
@@ -3540,24 +3753,27 @@
         <v>1.2</v>
       </c>
       <c r="G72" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H72" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I72" s="6" t="n">
         <v>1.281</v>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="J72" s="6" t="n">
         <v>1.436</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="K72" s="6" t="n">
         <v>1.632</v>
       </c>
-      <c r="K72" s="7" t="n">
+      <c r="L72" s="7" t="n">
         <v>98.47</v>
       </c>
-      <c r="L72" s="7" t="n">
+      <c r="M72" s="7" t="n">
         <v>143.6</v>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="N72" s="7" t="n">
         <v>200.06</v>
       </c>
     </row>
@@ -3575,7 +3791,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3585,25 +3801,28 @@
         <v>1.7</v>
       </c>
       <c r="G73" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>2.571</v>
+        <v>3.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.5</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>2.88</v>
+        <v>3.844</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>3.275</v>
-      </c>
-      <c r="K73" s="7" t="n">
-        <v>197.63</v>
+        <v>4.307</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>4.897</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>288</v>
+        <v>295.49</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>401.46</v>
+        <v>430.7</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>600.29</v>
       </c>
     </row>
     <row r="74">
@@ -3620,7 +3839,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3630,25 +3849,28 @@
         <v>1.7</v>
       </c>
       <c r="G74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>2.104</v>
+        <v>2.75</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.5</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>2.357</v>
+        <v>2.936</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K74" s="7" t="n">
-        <v>161.73</v>
+        <v>3.29</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>3.741</v>
       </c>
       <c r="L74" s="7" t="n">
-        <v>235.7</v>
+        <v>225.69</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>328.52</v>
+        <v>329</v>
+      </c>
+      <c r="N74" s="7" t="n">
+        <v>458.58</v>
       </c>
     </row>
     <row r="75">
@@ -3674,22 +3896,25 @@
       <c r="G75" t="n">
         <v>1.5</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I75" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="J75" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="K75" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K75" s="7" t="n">
+      <c r="L75" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L75" s="7" t="n">
+      <c r="M75" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="N75" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -3714,24 +3939,27 @@
         <v>9.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H76" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I76" s="6" t="n">
         <v>10.143</v>
       </c>
-      <c r="I76" s="6" t="n">
+      <c r="J76" s="6" t="n">
         <v>11.365</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="K76" s="6" t="n">
         <v>12.923</v>
       </c>
-      <c r="K76" s="7" t="n">
+      <c r="L76" s="7" t="n">
         <v>779.6799999999999</v>
       </c>
-      <c r="L76" s="7" t="n">
+      <c r="M76" s="7" t="n">
         <v>1136.5</v>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="N76" s="7" t="n">
         <v>1584.14</v>
       </c>
     </row>
@@ -3759,24 +3987,27 @@
         <v>2.2</v>
       </c>
       <c r="G77" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H77" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I77" s="6" t="n">
         <v>2.349</v>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="J77" s="6" t="n">
         <v>2.632</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="K77" s="6" t="n">
         <v>2.993</v>
       </c>
-      <c r="K77" s="7" t="n">
+      <c r="L77" s="7" t="n">
         <v>180.57</v>
       </c>
-      <c r="L77" s="7" t="n">
+      <c r="M77" s="7" t="n">
         <v>263.2</v>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="N77" s="7" t="n">
         <v>366.89</v>
       </c>
     </row>
@@ -3801,24 +4032,27 @@
         <v>6.2</v>
       </c>
       <c r="G78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H78" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I78" s="6" t="n">
         <v>6.62</v>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="J78" s="6" t="n">
         <v>7.417</v>
       </c>
-      <c r="J78" s="6" t="n">
+      <c r="K78" s="6" t="n">
         <v>8.433999999999999</v>
       </c>
-      <c r="K78" s="7" t="n">
+      <c r="L78" s="7" t="n">
         <v>508.87</v>
       </c>
-      <c r="L78" s="7" t="n">
+      <c r="M78" s="7" t="n">
         <v>741.7</v>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="N78" s="7" t="n">
         <v>1033.87</v>
       </c>
     </row>
@@ -3845,22 +4079,25 @@
       <c r="G79" t="n">
         <v>1.5</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I79" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="J79" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="K79" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K79" s="7" t="n">
+      <c r="L79" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L79" s="7" t="n">
+      <c r="M79" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="N79" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -3885,24 +4122,27 @@
         <v>2.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H80" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I80" s="6" t="n">
         <v>2.669</v>
       </c>
-      <c r="I80" s="6" t="n">
+      <c r="J80" s="6" t="n">
         <v>2.991</v>
       </c>
-      <c r="J80" s="6" t="n">
+      <c r="K80" s="6" t="n">
         <v>3.401</v>
       </c>
-      <c r="K80" s="7" t="n">
+      <c r="L80" s="7" t="n">
         <v>205.16</v>
       </c>
-      <c r="L80" s="7" t="n">
+      <c r="M80" s="7" t="n">
         <v>299.1</v>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="N80" s="7" t="n">
         <v>416.91</v>
       </c>
     </row>
@@ -3920,7 +4160,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -3930,25 +4170,28 @@
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>5.431</v>
+        <v>6.3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.5</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>6.086</v>
+        <v>6.726</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K81" s="7" t="n">
-        <v>417.48</v>
+        <v>7.537</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>8.57</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>608.6</v>
+        <v>517.02</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>848.28</v>
+        <v>753.7</v>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>1050.54</v>
       </c>
     </row>
     <row r="82">
@@ -3975,24 +4218,27 @@
         <v>6</v>
       </c>
       <c r="G82" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H82" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I82" s="6" t="n">
         <v>6.406</v>
       </c>
-      <c r="I82" s="6" t="n">
+      <c r="J82" s="6" t="n">
         <v>7.178</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="K82" s="6" t="n">
         <v>8.162000000000001</v>
       </c>
-      <c r="K82" s="7" t="n">
+      <c r="L82" s="7" t="n">
         <v>492.42</v>
       </c>
-      <c r="L82" s="7" t="n">
+      <c r="M82" s="7" t="n">
         <v>717.8</v>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="N82" s="7" t="n">
         <v>1000.53</v>
       </c>
     </row>
@@ -4019,22 +4265,25 @@
       <c r="G83" t="n">
         <v>1.5</v>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I83" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I83" s="6" t="n">
+      <c r="J83" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J83" s="6" t="n">
+      <c r="K83" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="L83" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L83" s="7" t="n">
+      <c r="M83" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="N83" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -4059,24 +4308,27 @@
         <v>1.1</v>
       </c>
       <c r="G84" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H84" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I84" s="6" t="n">
         <v>1.174</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="J84" s="6" t="n">
         <v>1.316</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="K84" s="6" t="n">
         <v>1.496</v>
       </c>
-      <c r="K84" s="7" t="n">
+      <c r="L84" s="7" t="n">
         <v>90.23999999999999</v>
       </c>
-      <c r="L84" s="7" t="n">
+      <c r="M84" s="7" t="n">
         <v>131.6</v>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="N84" s="7" t="n">
         <v>183.38</v>
       </c>
     </row>
@@ -4094,7 +4346,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4104,25 +4356,28 @@
         <v>1.3</v>
       </c>
       <c r="G85" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>1.731</v>
+        <v>2.55</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.5</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.94</v>
+        <v>2.723</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>2.206</v>
-      </c>
-      <c r="K85" s="7" t="n">
-        <v>133.06</v>
+        <v>3.051</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>3.469</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>194</v>
+        <v>209.31</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>270.42</v>
+        <v>305.1</v>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>425.24</v>
       </c>
     </row>
     <row r="86">
@@ -4139,7 +4394,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4149,25 +4404,28 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H86" s="6" t="n">
-        <v>2.152</v>
+        <v>3.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.5</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>2.412</v>
+        <v>3.737</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="K86" s="7" t="n">
-        <v>165.42</v>
+        <v>4.187</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>4.761</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>241.2</v>
+        <v>287.26</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>336.12</v>
+        <v>418.7</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>583.62</v>
       </c>
     </row>
     <row r="87">
@@ -4184,7 +4442,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4194,25 +4452,28 @@
         <v>2.5</v>
       </c>
       <c r="G87" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>4.619</v>
+        <v>5.6</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.5</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>5.176</v>
+        <v>5.979</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>5.885</v>
-      </c>
-      <c r="K87" s="7" t="n">
-        <v>355.06</v>
+        <v>6.7</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>7.618</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>517.6</v>
+        <v>459.6</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>721.4</v>
+        <v>670</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>933.84</v>
       </c>
     </row>
     <row r="88">
@@ -4239,25 +4500,28 @@
         <v>2.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H88" s="6" t="n">
-        <v>6.947</v>
+        <v>6.25</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.15</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>7.785</v>
+        <v>9.565</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>8.851000000000001</v>
-      </c>
-      <c r="K88" s="7" t="n">
-        <v>534.01</v>
+        <v>10.717</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>12.186</v>
       </c>
       <c r="L88" s="7" t="n">
-        <v>778.5</v>
+        <v>735.25</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>1084.99</v>
+        <v>1071.7</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>1493.8</v>
       </c>
     </row>
     <row r="89">
@@ -4283,22 +4547,25 @@
       <c r="G89" t="n">
         <v>1.5</v>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I89" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I89" s="6" t="n">
+      <c r="J89" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="K89" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="L89" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L89" s="7" t="n">
+      <c r="M89" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="N89" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -4323,24 +4590,27 @@
         <v>6.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H90" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I90" s="6" t="n">
         <v>6.94</v>
       </c>
-      <c r="I90" s="6" t="n">
+      <c r="J90" s="6" t="n">
         <v>7.776</v>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="K90" s="6" t="n">
         <v>8.842000000000001</v>
       </c>
-      <c r="K90" s="7" t="n">
+      <c r="L90" s="7" t="n">
         <v>533.47</v>
       </c>
-      <c r="L90" s="7" t="n">
+      <c r="M90" s="7" t="n">
         <v>777.6</v>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="N90" s="7" t="n">
         <v>1083.88</v>
       </c>
     </row>
@@ -4358,7 +4628,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -4368,25 +4638,28 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H91" s="6" t="n">
-        <v>3.077</v>
+        <v>4.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.5</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>3.448</v>
+        <v>4.377</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="K91" s="7" t="n">
-        <v>236.53</v>
+        <v>4.905</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>5.577</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>344.8</v>
+        <v>336.46</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>480.53</v>
+        <v>490.5</v>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>683.65</v>
       </c>
     </row>
     <row r="92">
@@ -4410,24 +4683,27 @@
         <v>3.6</v>
       </c>
       <c r="G92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H92" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I92" s="6" t="n">
         <v>3.844</v>
       </c>
-      <c r="I92" s="6" t="n">
+      <c r="J92" s="6" t="n">
         <v>4.307</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="K92" s="6" t="n">
         <v>4.897</v>
       </c>
-      <c r="K92" s="7" t="n">
+      <c r="L92" s="7" t="n">
         <v>295.49</v>
       </c>
-      <c r="L92" s="7" t="n">
+      <c r="M92" s="7" t="n">
         <v>430.7</v>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="N92" s="7" t="n">
         <v>600.29</v>
       </c>
     </row>
@@ -4454,22 +4730,25 @@
       <c r="G93" t="n">
         <v>1.5</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I93" s="6" t="n">
         <v>1.602</v>
       </c>
-      <c r="I93" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>1.795</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="K93" s="6" t="n">
         <v>2.04</v>
       </c>
-      <c r="K93" s="7" t="n">
+      <c r="L93" s="7" t="n">
         <v>123.14</v>
       </c>
-      <c r="L93" s="7" t="n">
+      <c r="M93" s="7" t="n">
         <v>179.5</v>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="N93" s="7" t="n">
         <v>250.07</v>
       </c>
     </row>
@@ -4487,7 +4766,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>sivri</t>
+          <t>ort</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4497,25 +4776,28 @@
         <v>1.3</v>
       </c>
       <c r="G94" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H94" s="6" t="n">
-        <v>1.778</v>
+        <v>2.65</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.5</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>1.993</v>
+        <v>2.829</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>2.266</v>
-      </c>
-      <c r="K94" s="7" t="n">
-        <v>136.67</v>
+        <v>3.17</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>3.605</v>
       </c>
       <c r="L94" s="7" t="n">
-        <v>199.3</v>
+        <v>217.46</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>277.77</v>
+        <v>317</v>
+      </c>
+      <c r="N94" s="7" t="n">
+        <v>441.91</v>
       </c>
     </row>
     <row r="95">
@@ -4542,30 +4824,33 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I95" s="6" t="n">
         <v>1.068</v>
       </c>
-      <c r="I95" s="6" t="n">
+      <c r="J95" s="6" t="n">
         <v>1.196</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="K95" s="6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K95" s="7" t="n">
+      <c r="L95" s="7" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="L95" s="7" t="n">
+      <c r="M95" s="7" t="n">
         <v>119.6</v>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="N95" s="7" t="n">
         <v>166.71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7622,7 +7907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -7635,7 +7920,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -7724,6 +8008,16 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>Kaynak kod: scripts/ophir/gram_model.py (self_test ile dogrulanir).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>9) Sivrilen yuzuk (Top Width + Shank Width): etkin en = (ust+shank)/2; iki kalinlik varsa kalinlik = ortalamasi. SAHIBIN KURALI 2026-09-16 — onceki cevre-agirlikli taper modeli kaldirildi.</t>
         </is>
       </c>
     </row>
